--- a/crates/xlstream-eval/tests/fixtures/text/concat.xlsx
+++ b/crates/xlstream-eval/tests/fixtures/text/concat.xlsx
@@ -20,60 +20,69 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="18">
-  <si>
-    <t xml:space="preserve">region</t>
-  </si>
-  <si>
-    <t xml:space="preserve">text</t>
-  </si>
-  <si>
-    <t xml:space="preserve">concat</t>
-  </si>
-  <si>
-    <t xml:space="preserve">concatenate</t>
-  </si>
-  <si>
-    <t xml:space="preserve">textjoin</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EMEA</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="21">
+  <si>
+    <t xml:space="preserve">a</t>
+  </si>
+  <si>
+    <t xml:space="preserve">b</t>
+  </si>
+  <si>
+    <t xml:space="preserve">concat_ab</t>
+  </si>
+  <si>
+    <t xml:space="preserve">concatenate_ab</t>
+  </si>
+  <si>
+    <t xml:space="preserve">textjoin_dash</t>
+  </si>
+  <si>
+    <t xml:space="preserve">concat_num</t>
+  </si>
+  <si>
+    <t xml:space="preserve">textjoin_skip_empty</t>
   </si>
   <si>
     <t xml:space="preserve">hello</t>
   </si>
   <si>
-    <t xml:space="preserve">APAC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">WORLD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AMER</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  spaces  here  </t>
+    <t xml:space="preserve">world</t>
+  </si>
+  <si>
+    <t xml:space="preserve">foo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">bar</t>
+  </si>
+  <si>
+    <t xml:space="preserve">test</t>
   </si>
   <si>
     <t xml:space="preserve">abc</t>
   </si>
   <si>
-    <t xml:space="preserve">short</t>
-  </si>
-  <si>
-    <t xml:space="preserve">test</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ProPer Case</t>
-  </si>
-  <si>
-    <t xml:space="preserve">num123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">foo bar</t>
+    <t xml:space="preserve">A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">B</t>
+  </si>
+  <si>
+    <t xml:space="preserve">123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">456</t>
+  </si>
+  <si>
+    <t xml:space="preserve">long</t>
+  </si>
+  <si>
+    <t xml:space="preserve">string</t>
   </si>
   <si>
     <t xml:space="preserve">x</t>
+  </si>
+  <si>
+    <t xml:space="preserve">y</t>
   </si>
 </sst>
 </file>
@@ -346,7 +355,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:E11"/>
+  <dimension ref="A1:G9"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -365,205 +374,229 @@
       <c r="E1" s="0" t="s">
         <v>4</v>
       </c>
+      <c r="F1" s="0" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="0" t="s">
+        <v>6</v>
+      </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="0" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="B2" s="0" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C2" s="0" t="str">
-        <f aca="false">_xlfn.CONCAT(A2,"-",B2)</f>
-        <v>EMEA-hello</v>
+        <f aca="false">_xlfn.CONCAT(A2,B2)</f>
+        <v>helloworld</v>
       </c>
       <c r="D2" s="0" t="str">
-        <f aca="false">CONCATENATE(A2,"-",B2)</f>
-        <v>EMEA-hello</v>
+        <f aca="false">CONCATENATE(A2,B2)</f>
+        <v>helloworld</v>
       </c>
       <c r="E2" s="0" t="str">
         <f aca="false">_xlfn.TEXTJOIN("-",TRUE(),A2,B2)</f>
-        <v>EMEA-hello</v>
+        <v>hello-world</v>
+      </c>
+      <c r="F2" s="0" t="str">
+        <f aca="false">_xlfn.CONCAT(A2,"-",B2)</f>
+        <v>hello-world</v>
+      </c>
+      <c r="G2" s="0" t="str">
+        <f aca="false">_xlfn.TEXTJOIN(",",TRUE(),A2,"",B2)</f>
+        <v>hello,world</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="0" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="B3" s="0" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C3" s="0" t="str">
-        <f aca="false">_xlfn.CONCAT(A3,"-",B3)</f>
-        <v>APAC-WORLD</v>
+        <f aca="false">_xlfn.CONCAT(A3,B3)</f>
+        <v>foobar</v>
       </c>
       <c r="D3" s="0" t="str">
-        <f aca="false">CONCATENATE(A3,"-",B3)</f>
-        <v>APAC-WORLD</v>
+        <f aca="false">CONCATENATE(A3,B3)</f>
+        <v>foobar</v>
       </c>
       <c r="E3" s="0" t="str">
         <f aca="false">_xlfn.TEXTJOIN("-",TRUE(),A3,B3)</f>
-        <v>APAC-WORLD</v>
+        <v>foo-bar</v>
+      </c>
+      <c r="F3" s="0" t="str">
+        <f aca="false">_xlfn.CONCAT(A3,"-",B3)</f>
+        <v>foo-bar</v>
+      </c>
+      <c r="G3" s="0" t="str">
+        <f aca="false">_xlfn.TEXTJOIN(",",TRUE(),A3,"",B3)</f>
+        <v>foo,bar</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="0" t="s">
-        <v>9</v>
-      </c>
       <c r="B4" s="0" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C4" s="0" t="str">
-        <f aca="false">_xlfn.CONCAT(A4,"-",B4)</f>
-        <v>AMER-  spaces  here  </v>
+        <f aca="false">_xlfn.CONCAT(A4,B4)</f>
+        <v>test</v>
       </c>
       <c r="D4" s="0" t="str">
-        <f aca="false">CONCATENATE(A4,"-",B4)</f>
-        <v>AMER-  spaces  here  </v>
+        <f aca="false">CONCATENATE(A4,B4)</f>
+        <v>test</v>
       </c>
       <c r="E4" s="0" t="str">
         <f aca="false">_xlfn.TEXTJOIN("-",TRUE(),A4,B4)</f>
-        <v>AMER-  spaces  here  </v>
+        <v>test</v>
+      </c>
+      <c r="F4" s="0" t="str">
+        <f aca="false">_xlfn.CONCAT(A4,"-",B4)</f>
+        <v>-test</v>
+      </c>
+      <c r="G4" s="0" t="str">
+        <f aca="false">_xlfn.TEXTJOIN(",",TRUE(),A4,"",B4)</f>
+        <v>test</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="0" t="s">
-        <v>5</v>
-      </c>
-      <c r="B5" s="0" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C5" s="0" t="str">
-        <f aca="false">_xlfn.CONCAT(A5,"-",B5)</f>
-        <v>EMEA-abc</v>
+        <f aca="false">_xlfn.CONCAT(A5,B5)</f>
+        <v>abc</v>
       </c>
       <c r="D5" s="0" t="str">
-        <f aca="false">CONCATENATE(A5,"-",B5)</f>
-        <v>EMEA-abc</v>
+        <f aca="false">CONCATENATE(A5,B5)</f>
+        <v>abc</v>
       </c>
       <c r="E5" s="0" t="str">
         <f aca="false">_xlfn.TEXTJOIN("-",TRUE(),A5,B5)</f>
-        <v>EMEA-abc</v>
+        <v>abc</v>
+      </c>
+      <c r="F5" s="0" t="str">
+        <f aca="false">_xlfn.CONCAT(A5,"-",B5)</f>
+        <v>abc-</v>
+      </c>
+      <c r="G5" s="0" t="str">
+        <f aca="false">_xlfn.TEXTJOIN(",",TRUE(),A5,"",B5)</f>
+        <v>abc</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="0" t="s">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="B6" s="0" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C6" s="0" t="str">
-        <f aca="false">_xlfn.CONCAT(A6,"-",B6)</f>
-        <v>APAC-short</v>
+        <f aca="false">_xlfn.CONCAT(A6,B6)</f>
+        <v>AB</v>
       </c>
       <c r="D6" s="0" t="str">
-        <f aca="false">CONCATENATE(A6,"-",B6)</f>
-        <v>APAC-short</v>
+        <f aca="false">CONCATENATE(A6,B6)</f>
+        <v>AB</v>
       </c>
       <c r="E6" s="0" t="str">
         <f aca="false">_xlfn.TEXTJOIN("-",TRUE(),A6,B6)</f>
-        <v>APAC-short</v>
+        <v>A-B</v>
+      </c>
+      <c r="F6" s="0" t="str">
+        <f aca="false">_xlfn.CONCAT(A6,"-",B6)</f>
+        <v>A-B</v>
+      </c>
+      <c r="G6" s="0" t="str">
+        <f aca="false">_xlfn.TEXTJOIN(",",TRUE(),A6,"",B6)</f>
+        <v>A,B</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="0" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="B7" s="0" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="C7" s="0" t="str">
-        <f aca="false">_xlfn.CONCAT(A7,"-",B7)</f>
-        <v>AMER-test</v>
+        <f aca="false">_xlfn.CONCAT(A7,B7)</f>
+        <v>123456</v>
       </c>
       <c r="D7" s="0" t="str">
-        <f aca="false">CONCATENATE(A7,"-",B7)</f>
-        <v>AMER-test</v>
+        <f aca="false">CONCATENATE(A7,B7)</f>
+        <v>123456</v>
       </c>
       <c r="E7" s="0" t="str">
         <f aca="false">_xlfn.TEXTJOIN("-",TRUE(),A7,B7)</f>
-        <v>AMER-test</v>
+        <v>123-456</v>
+      </c>
+      <c r="F7" s="0" t="str">
+        <f aca="false">_xlfn.CONCAT(A7,"-",B7)</f>
+        <v>123-456</v>
+      </c>
+      <c r="G7" s="0" t="str">
+        <f aca="false">_xlfn.TEXTJOIN(",",TRUE(),A7,"",B7)</f>
+        <v>123,456</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="0" t="s">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="B8" s="0" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="C8" s="0" t="str">
-        <f aca="false">_xlfn.CONCAT(A8,"-",B8)</f>
-        <v>EMEA-ProPer Case</v>
+        <f aca="false">_xlfn.CONCAT(A8,B8)</f>
+        <v>longstring</v>
       </c>
       <c r="D8" s="0" t="str">
-        <f aca="false">CONCATENATE(A8,"-",B8)</f>
-        <v>EMEA-ProPer Case</v>
+        <f aca="false">CONCATENATE(A8,B8)</f>
+        <v>longstring</v>
       </c>
       <c r="E8" s="0" t="str">
         <f aca="false">_xlfn.TEXTJOIN("-",TRUE(),A8,B8)</f>
-        <v>EMEA-ProPer Case</v>
+        <v>long-string</v>
+      </c>
+      <c r="F8" s="0" t="str">
+        <f aca="false">_xlfn.CONCAT(A8,"-",B8)</f>
+        <v>long-string</v>
+      </c>
+      <c r="G8" s="0" t="str">
+        <f aca="false">_xlfn.TEXTJOIN(",",TRUE(),A8,"",B8)</f>
+        <v>long,string</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="0" t="s">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="B9" s="0" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="C9" s="0" t="str">
-        <f aca="false">_xlfn.CONCAT(A9,"-",B9)</f>
-        <v>APAC-num123</v>
+        <f aca="false">_xlfn.CONCAT(A9,B9)</f>
+        <v>xy</v>
       </c>
       <c r="D9" s="0" t="str">
-        <f aca="false">CONCATENATE(A9,"-",B9)</f>
-        <v>APAC-num123</v>
+        <f aca="false">CONCATENATE(A9,B9)</f>
+        <v>xy</v>
       </c>
       <c r="E9" s="0" t="str">
         <f aca="false">_xlfn.TEXTJOIN("-",TRUE(),A9,B9)</f>
-        <v>APAC-num123</v>
-      </c>
-    </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="0" t="s">
-        <v>9</v>
-      </c>
-      <c r="B10" s="0" t="s">
-        <v>16</v>
-      </c>
-      <c r="C10" s="0" t="str">
-        <f aca="false">_xlfn.CONCAT(A10,"-",B10)</f>
-        <v>AMER-foo bar</v>
-      </c>
-      <c r="D10" s="0" t="str">
-        <f aca="false">CONCATENATE(A10,"-",B10)</f>
-        <v>AMER-foo bar</v>
-      </c>
-      <c r="E10" s="0" t="str">
-        <f aca="false">_xlfn.TEXTJOIN("-",TRUE(),A10,B10)</f>
-        <v>AMER-foo bar</v>
-      </c>
-    </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="0" t="s">
-        <v>5</v>
-      </c>
-      <c r="B11" s="0" t="s">
-        <v>17</v>
-      </c>
-      <c r="C11" s="0" t="str">
-        <f aca="false">_xlfn.CONCAT(A11,"-",B11)</f>
-        <v>EMEA-x</v>
-      </c>
-      <c r="D11" s="0" t="str">
-        <f aca="false">CONCATENATE(A11,"-",B11)</f>
-        <v>EMEA-x</v>
-      </c>
-      <c r="E11" s="0" t="str">
-        <f aca="false">_xlfn.TEXTJOIN("-",TRUE(),A11,B11)</f>
-        <v>EMEA-x</v>
+        <v>x-y</v>
+      </c>
+      <c r="F9" s="0" t="str">
+        <f aca="false">_xlfn.CONCAT(A9,"-",B9)</f>
+        <v>x-y</v>
+      </c>
+      <c r="G9" s="0" t="str">
+        <f aca="false">_xlfn.TEXTJOIN(",",TRUE(),A9,"",B9)</f>
+        <v>x,y</v>
       </c>
     </row>
   </sheetData>
